--- a/Методы и средства криптографической защ инф/Лаба 4/Лаба 4.xlsx
+++ b/Методы и средства криптографической защ инф/Лаба 4/Лаба 4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ForMi\OneDrive\Desktop\Fourth_course\Методы и средства криптографической защ инф\Лаба 4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE4A574D-5A1B-4153-B2BC-71E6045E8585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF0C8FBE-6043-43A8-A712-0A2A006D586D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Вижинера" sheetId="1" r:id="rId1"/>
@@ -315,9 +315,6 @@
     <t xml:space="preserve"> Э</t>
   </si>
   <si>
-    <t>МЪ</t>
-  </si>
-  <si>
     <t>З. Биграммы:</t>
   </si>
   <si>
@@ -429,9 +426,6 @@
     <t>ЦШ</t>
   </si>
   <si>
-    <t>ЗД</t>
-  </si>
-  <si>
     <t>ПК</t>
   </si>
   <si>
@@ -448,6 +442,12 @@
   </si>
   <si>
     <t>С:УДМЖЦЪЕМФМОА.М.ЮХБДЦПСХГФЫЛ ,ХХЛВА:РЖБГЖЬЪНТЦСЧУВЬУЪБЮОБЕБЛАС:ЫЫЗТПР.ЫПКБЩ,ЩПШЦЧ.ЫГЖЩХЪЛЦШЖБЗД</t>
+  </si>
+  <si>
+    <t>М.</t>
+  </si>
+  <si>
+    <t>ВД</t>
   </si>
 </sst>
 </file>
@@ -504,7 +504,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -512,35 +512,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -821,19 +811,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:CT16"/>
+  <dimension ref="B2:CS15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="17.28515625" customWidth="1"/>
     <col min="3" max="97" width="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:98" x14ac:dyDescent="0.25">
-      <c r="B2" s="8" t="s">
+    <row r="2" spans="2:97" x14ac:dyDescent="0.25">
+      <c r="B2" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="2:98" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:97" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>32</v>
       </c>
@@ -841,11 +831,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:98" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:97" x14ac:dyDescent="0.25">
       <c r="B4" s="1"/>
     </row>
-    <row r="5" spans="2:98" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="5" t="s">
+    <row r="5" spans="2:97" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="4" t="s">
         <v>32</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -1007,49 +997,49 @@
       <c r="BC5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="BD5" s="3" t="s">
+      <c r="BD5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="BE5" s="3" t="s">
+      <c r="BE5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="BF5" s="3" t="s">
+      <c r="BF5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="BG5" s="3" t="s">
+      <c r="BG5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="BH5" s="3" t="s">
+      <c r="BH5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="BI5" s="3" t="s">
+      <c r="BI5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="BJ5" s="3" t="s">
+      <c r="BJ5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="BK5" s="3" t="s">
+      <c r="BK5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="BL5" s="3" t="s">
+      <c r="BL5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="BM5" s="3" t="s">
+      <c r="BM5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="BN5" s="3" t="s">
+      <c r="BN5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="BO5" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="BP5" s="3" t="s">
+      <c r="BO5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="BP5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="BQ5" s="3" t="s">
+      <c r="BQ5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="BR5" s="3" t="s">
+      <c r="BR5" s="2" t="s">
         <v>25</v>
       </c>
       <c r="BS5" s="2" t="s">
@@ -1082,60 +1072,60 @@
       <c r="CB5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="CC5" s="3" t="s">
+      <c r="CC5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="CD5" s="3" t="s">
+      <c r="CD5" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="CE5" s="3" t="s">
+      <c r="CE5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="CF5" s="3" t="s">
+      <c r="CF5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="CG5" s="3" t="s">
+      <c r="CG5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="CH5" s="3" t="s">
+      <c r="CH5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="CI5" s="3" t="s">
+      <c r="CI5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="CJ5" s="3" t="s">
+      <c r="CJ5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="CK5" s="3" t="s">
+      <c r="CK5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="CL5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="CM5" s="3" t="s">
+      <c r="CM5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="CN5" s="3" t="s">
+      <c r="CN5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="CO5" s="3" t="s">
+      <c r="CO5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="CP5" s="3" t="s">
+      <c r="CP5" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="CQ5" s="3" t="s">
+      <c r="CQ5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="CR5" s="3" t="s">
+      <c r="CR5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="CS5" s="3" t="s">
+      <c r="CS5" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="2:98" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="5" t="s">
+    <row r="6" spans="2:97" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="4" t="s">
         <v>45</v>
       </c>
       <c r="C6" s="2">
@@ -1388,8 +1378,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="2:98" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="5" t="s">
+    <row r="7" spans="2:97" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="4" t="s">
         <v>33</v>
       </c>
       <c r="C7" s="2" t="s">
@@ -1642,8 +1632,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="2:98" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="5" t="s">
+    <row r="8" spans="2:97" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="4" t="s">
         <v>34</v>
       </c>
       <c r="C8" s="2">
@@ -1888,10 +1878,9 @@
       <c r="CS8" s="2">
         <v>4</v>
       </c>
-      <c r="CT8" s="4"/>
     </row>
-    <row r="9" spans="2:98" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="5" t="s">
+    <row r="9" spans="2:97" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="4" t="s">
         <v>35</v>
       </c>
       <c r="C9" s="2">
@@ -1899,7 +1888,7 @@
         <v>22</v>
       </c>
       <c r="D9" s="2">
-        <f t="shared" ref="D9:BO9" si="0">MOD(D6+D8,32)</f>
+        <f t="shared" ref="D9:H9" si="0">MOD(D6+D8,32)</f>
         <v>29</v>
       </c>
       <c r="E9" s="2">
@@ -2221,8 +2210,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="2:98" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="5" t="s">
+    <row r="10" spans="2:97" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="4" t="s">
         <v>36</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -2475,10 +2464,10 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="2:98" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:97" x14ac:dyDescent="0.25">
       <c r="B11" s="1"/>
     </row>
-    <row r="12" spans="2:98" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:97" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
         <v>36</v>
       </c>
@@ -2486,7 +2475,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="2:98" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:97" x14ac:dyDescent="0.25">
       <c r="D14" s="2">
         <v>0</v>
       </c>
@@ -2741,12 +2730,12 @@
         <f t="shared" ref="CK14" si="123">CJ14+1</f>
         <v>31</v>
       </c>
-      <c r="CL14" s="4"/>
-      <c r="CM14" s="4"/>
-      <c r="CN14" s="4"/>
-      <c r="CO14" s="4"/>
+      <c r="CL14" s="3"/>
+      <c r="CM14" s="3"/>
+      <c r="CN14" s="3"/>
+      <c r="CO14" s="3"/>
     </row>
-    <row r="15" spans="2:98" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:97" x14ac:dyDescent="0.25">
       <c r="D15" s="2" t="s">
         <v>4</v>
       </c>
@@ -2939,12 +2928,7 @@
       <c r="CK15" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="CO15" s="4"/>
-      <c r="CP15" s="7"/>
-    </row>
-    <row r="16" spans="2:98" x14ac:dyDescent="0.25">
-      <c r="CO16" s="7"/>
-      <c r="CP16" s="7"/>
+      <c r="CO15" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3023,20 +3007,20 @@
     </row>
     <row r="6" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B6" s="1"/>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="J6" s="10" t="s">
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="J6" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="K6" s="10"/>
-      <c r="L6" s="10"/>
-      <c r="M6" s="10"/>
-      <c r="N6" s="10"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="9"/>
       <c r="P6" t="s">
         <v>49</v>
       </c>
@@ -3185,387 +3169,389 @@
         <v>69</v>
       </c>
       <c r="BK7" s="2" t="s">
-        <v>92</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B8" s="1"/>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J8" s="3" t="s">
+      <c r="H8" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="K8" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="L8" s="3" t="s">
+      <c r="L8" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="M8" s="3" t="s">
+      <c r="M8" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="N8" s="3" t="s">
+      <c r="N8" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="P8" s="11"/>
+      <c r="P8" s="6"/>
     </row>
     <row r="9" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B9" s="1"/>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="H9" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="J9" s="3" t="s">
+      <c r="J9" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="K9" s="3" t="s">
+      <c r="K9" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="L9" s="3" t="s">
+      <c r="L9" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="M9" s="3" t="s">
+      <c r="M9" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="N9" s="3" t="s">
+      <c r="N9" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="P9" s="11" t="s">
-        <v>93</v>
+      <c r="P9" s="6" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B10" s="1"/>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="G10" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="H10" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="J10" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="K10" s="3" t="s">
+      <c r="K10" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M10" s="3" t="s">
+      <c r="L10" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="M10" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="N10" s="3" t="s">
+      <c r="N10" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="P10" s="3" t="s">
+      <c r="P10" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q10" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="Q10" s="3" t="s">
+      <c r="R10" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="R10" s="3" t="s">
+      <c r="S10" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="S10" s="3" t="s">
+      <c r="T10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="U10" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="U10" s="3" t="s">
+      <c r="V10" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="V10" s="3" t="s">
+      <c r="W10" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="W10" s="3" t="s">
+      <c r="X10" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="X10" s="3" t="s">
+      <c r="Y10" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="Y10" s="3" t="s">
+      <c r="Z10" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="Z10" s="3" t="s">
+      <c r="AA10" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="AA10" s="3" t="s">
+      <c r="AB10" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="AB10" s="3" t="s">
+      <c r="AC10" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="AC10" s="3" t="s">
+      <c r="AD10" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="AD10" s="3" t="s">
+      <c r="AE10" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="AE10" s="3" t="s">
+      <c r="AF10" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="AF10" s="3" t="s">
+      <c r="AG10" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="AG10" s="3" t="s">
+      <c r="AH10" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="AH10" s="3" t="s">
+      <c r="AI10" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="AI10" s="3" t="s">
+      <c r="AJ10" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="AJ10" s="3" t="s">
+      <c r="AK10" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="AK10" s="3" t="s">
+      <c r="AL10" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="AL10" s="3" t="s">
+      <c r="AM10" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="AM10" s="3" t="s">
+      <c r="AN10" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="AN10" s="3" t="s">
+      <c r="AO10" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="AO10" s="3" t="s">
+      <c r="AP10" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="AP10" s="3" t="s">
+      <c r="AQ10" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="AQ10" s="3" t="s">
+      <c r="AR10" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="AS10" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="AR10" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="AS10" s="3" t="s">
+      <c r="AT10" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="AT10" s="3" t="s">
+      <c r="AU10" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AV10" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="AU10" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="AV10" s="3" t="s">
+      <c r="AW10" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="AW10" s="3" t="s">
+      <c r="AX10" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="AX10" s="3" t="s">
+      <c r="AY10" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="AY10" s="3" t="s">
+      <c r="AZ10" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="BA10" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="BB10" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="BC10" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="BD10" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="BE10" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="BF10" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="BG10" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="AZ10" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="BA10" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="BB10" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="BC10" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="BD10" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="BE10" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="BF10" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="BG10" s="3" t="s">
+      <c r="BH10" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="BH10" s="3" t="s">
+      <c r="BI10" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="BI10" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="BJ10" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="BK10" s="3" t="s">
-        <v>130</v>
+      <c r="BJ10" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="BK10" s="2" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="11" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B11" s="1"/>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="G11" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="H11" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="J11" s="3" t="s">
+      <c r="I11" s="8"/>
+      <c r="J11" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="K11" s="3" t="s">
+      <c r="K11" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="L11" s="3" t="s">
+      <c r="L11" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="M11" s="3" t="s">
+      <c r="M11" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="N11" s="3" t="s">
+      <c r="N11" s="7" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="12" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B12" s="1"/>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="E12" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F12" s="12" t="s">
+      <c r="F12" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="G12" s="12" t="s">
+      <c r="G12" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="H12" s="12" t="s">
+      <c r="H12" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="I12" s="13"/>
-      <c r="J12" s="12" t="s">
+      <c r="I12" s="8"/>
+      <c r="J12" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="K12" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="L12" s="12" t="s">
+      <c r="K12" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="L12" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="M12" s="3" t="s">
+      <c r="M12" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="N12" s="3" t="s">
+      <c r="N12" s="7" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="13" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B13" s="1"/>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="E13" s="12" t="s">
+      <c r="E13" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="F13" s="12" t="s">
+      <c r="F13" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G13" s="12" t="s">
+      <c r="G13" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H13" s="12" t="s">
+      <c r="H13" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="I13" s="13"/>
-      <c r="J13" s="12" t="s">
+      <c r="I13" s="8"/>
+      <c r="J13" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="K13" s="12" t="s">
+      <c r="K13" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="L13" s="12" t="s">
+      <c r="L13" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="M13" s="3" t="s">
+      <c r="M13" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="N13" s="3" t="s">
+      <c r="N13" s="7" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="14" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B14" s="1"/>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F14" s="2" t="s">
+      <c r="E14" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="G14" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="H14" s="2" t="s">
+      <c r="H14" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="I14" s="8"/>
+      <c r="J14" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="K14" s="3" t="s">
+      <c r="K14" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L14" s="3" t="s">
+      <c r="L14" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="M14" s="3" t="s">
+      <c r="M14" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3" t="s">
+      <c r="N14" s="7" t="s">
         <v>26</v>
       </c>
     </row>
@@ -3574,19 +3560,19 @@
     </row>
     <row r="16" spans="2:63" x14ac:dyDescent="0.25">
       <c r="B16" s="1"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
         <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
